--- a/comp130-schedule-9-6-2025.xlsx
+++ b/comp130-schedule-9-6-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmac\git\comp130-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB3B7A8-6BD7-4499-8330-D0DD922484D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2E1244-5BFE-4E61-A075-E3B22211B59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -744,7 +744,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>; Turtle; for loops</t>
+      <t xml:space="preserve">; Turtle; </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>for loops</t>
     </r>
   </si>
 </sst>
@@ -1072,6 +1083,57 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1084,59 +1146,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1478,7 +1489,7 @@
       <c r="D2" s="12">
         <v>1</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="27" t="s">
         <v>44</v>
       </c>
       <c r="F2" s="14" t="s">
@@ -1501,7 +1512,7 @@
         <f t="shared" ref="D3:D27" si="0">D2+1</f>
         <v>2</v>
       </c>
-      <c r="E3" s="34"/>
+      <c r="E3" s="28"/>
       <c r="F3" s="14" t="s">
         <v>158</v>
       </c>
@@ -1520,7 +1531,7 @@
         <v>45904</v>
       </c>
       <c r="D4" s="12"/>
-      <c r="E4" s="34"/>
+      <c r="E4" s="28"/>
       <c r="F4" s="14"/>
       <c r="G4" s="15"/>
       <c r="H4" s="14" t="s">
@@ -1541,7 +1552,7 @@
         <f>D3+1</f>
         <v>3</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="14" t="s">
         <v>159</v>
       </c>
@@ -1567,7 +1578,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="27" t="s">
         <v>78</v>
       </c>
       <c r="F6" s="14" t="s">
@@ -1595,7 +1606,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E7" s="34"/>
+      <c r="E7" s="28"/>
       <c r="F7" s="14" t="s">
         <v>163</v>
       </c>
@@ -1613,7 +1624,7 @@
         <v>45911</v>
       </c>
       <c r="D8" s="12"/>
-      <c r="E8" s="34"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="14"/>
       <c r="G8" s="15"/>
       <c r="H8" s="14" t="s">
@@ -1637,7 +1648,7 @@
         <f>D7+1</f>
         <v>6</v>
       </c>
-      <c r="E9" s="35"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="14" t="s">
         <v>160</v>
       </c>
@@ -1663,7 +1674,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="26" t="s">
         <v>79</v>
       </c>
       <c r="F10" s="14" t="s">
@@ -1676,7 +1687,7 @@
       <c r="I10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="Q10" s="29"/>
+      <c r="Q10" s="46"/>
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
@@ -1692,14 +1703,14 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E11" s="32"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="14" t="s">
         <v>101</v>
       </c>
       <c r="G11" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="Q11" s="29"/>
+      <c r="Q11" s="46"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="30"/>
@@ -1711,7 +1722,7 @@
         <v>45918</v>
       </c>
       <c r="D12" s="12"/>
-      <c r="E12" s="32"/>
+      <c r="E12" s="26"/>
       <c r="F12" s="14"/>
       <c r="G12" s="15"/>
       <c r="H12" s="14" t="s">
@@ -1720,7 +1731,7 @@
       <c r="I12" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="Q12" s="29"/>
+      <c r="Q12" s="46"/>
     </row>
     <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
@@ -1736,7 +1747,7 @@
         <f>D11+1</f>
         <v>9</v>
       </c>
-      <c r="E13" s="32"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="14" t="s">
         <v>102</v>
       </c>
@@ -1745,7 +1756,7 @@
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="12"/>
-      <c r="Q13" s="29"/>
+      <c r="Q13" s="46"/>
     </row>
     <row r="14" spans="1:17" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
@@ -1789,7 +1800,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="26" t="s">
         <v>81</v>
       </c>
       <c r="F15" s="14" t="s">
@@ -1809,7 +1820,7 @@
         <v>45925</v>
       </c>
       <c r="D16" s="12"/>
-      <c r="E16" s="32"/>
+      <c r="E16" s="26"/>
       <c r="F16" s="14"/>
       <c r="G16" s="15" t="s">
         <v>156</v>
@@ -1835,7 +1846,7 @@
         <f>D15+1</f>
         <v>12</v>
       </c>
-      <c r="E17" s="32"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="14" t="s">
         <v>103</v>
       </c>
@@ -1887,7 +1898,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="26" t="s">
         <v>80</v>
       </c>
       <c r="F19" s="14" t="s">
@@ -1907,7 +1918,7 @@
         <v>45932</v>
       </c>
       <c r="D20" s="12"/>
-      <c r="E20" s="32"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="14"/>
       <c r="G20" s="15"/>
       <c r="H20" s="14" t="s">
@@ -1931,7 +1942,7 @@
         <f>D19+1</f>
         <v>15</v>
       </c>
-      <c r="E21" s="32"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="20" t="s">
         <v>105</v>
       </c>
@@ -2046,7 +2057,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="26" t="s">
         <v>150</v>
       </c>
       <c r="F26" s="14" t="s">
@@ -2074,7 +2085,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="E27" s="32"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="14" t="s">
         <v>131</v>
       </c>
@@ -2093,7 +2104,7 @@
         <v>45946</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="32"/>
+      <c r="E28" s="26"/>
       <c r="F28" s="14"/>
       <c r="G28" s="15"/>
       <c r="H28" s="17" t="s">
@@ -2115,7 +2126,7 @@
         <f>D27+1</f>
         <v>21</v>
       </c>
-      <c r="E29" s="32"/>
+      <c r="E29" s="26"/>
       <c r="F29" s="14" t="s">
         <v>132</v>
       </c>
@@ -2129,16 +2140,16 @@
       <c r="A30" s="30">
         <v>8</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="38"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="30"/>
@@ -2154,7 +2165,7 @@
         <f>D29+1</f>
         <v>22</v>
       </c>
-      <c r="E31" s="32"/>
+      <c r="E31" s="26"/>
       <c r="F31" s="20" t="s">
         <v>96</v>
       </c>
@@ -2195,7 +2206,7 @@
         <f>D31+1</f>
         <v>23</v>
       </c>
-      <c r="E33" s="32" t="s">
+      <c r="E33" s="26" t="s">
         <v>83</v>
       </c>
       <c r="F33" s="14" t="s">
@@ -2225,7 +2236,7 @@
         <f t="shared" ref="D34:D50" si="7">D33+1</f>
         <v>24</v>
       </c>
-      <c r="E34" s="32"/>
+      <c r="E34" s="26"/>
       <c r="F34" s="14" t="s">
         <v>109</v>
       </c>
@@ -2249,7 +2260,7 @@
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
-      <c r="E35" s="32"/>
+      <c r="E35" s="26"/>
       <c r="F35" s="14" t="s">
         <v>108</v>
       </c>
@@ -2291,7 +2302,7 @@
         <f>D35+1</f>
         <v>26</v>
       </c>
-      <c r="E37" s="33" t="s">
+      <c r="E37" s="27" t="s">
         <v>84</v>
       </c>
       <c r="F37" s="14" t="s">
@@ -2321,7 +2332,7 @@
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
-      <c r="E38" s="34"/>
+      <c r="E38" s="28"/>
       <c r="F38" s="14" t="s">
         <v>111</v>
       </c>
@@ -2345,7 +2356,7 @@
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="E39" s="35"/>
+      <c r="E39" s="29"/>
       <c r="F39" s="14" t="s">
         <v>103</v>
       </c>
@@ -2386,7 +2397,7 @@
         <f>D39+1</f>
         <v>29</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="27" t="s">
         <v>85</v>
       </c>
       <c r="F41" s="14" t="s">
@@ -2416,7 +2427,7 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="E42" s="35"/>
+      <c r="E42" s="29"/>
       <c r="F42" s="14" t="s">
         <v>113</v>
       </c>
@@ -2440,7 +2451,7 @@
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
-      <c r="E43" s="32" t="s">
+      <c r="E43" s="26" t="s">
         <v>86</v>
       </c>
       <c r="F43" s="14" t="s">
@@ -2460,7 +2471,7 @@
         <v>45974</v>
       </c>
       <c r="D44" s="12"/>
-      <c r="E44" s="32"/>
+      <c r="E44" s="26"/>
       <c r="F44" s="14"/>
       <c r="G44" s="15"/>
       <c r="H44" s="14" t="s">
@@ -2484,7 +2495,7 @@
         <f>D43+1</f>
         <v>32</v>
       </c>
-      <c r="E45" s="32"/>
+      <c r="E45" s="26"/>
       <c r="F45" s="14" t="s">
         <v>115</v>
       </c>
@@ -2512,7 +2523,7 @@
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
-      <c r="E46" s="32"/>
+      <c r="E46" s="26"/>
       <c r="F46" s="14" t="s">
         <v>116</v>
       </c>
@@ -2601,7 +2612,7 @@
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="E50" s="32" t="s">
+      <c r="E50" s="26" t="s">
         <v>87</v>
       </c>
       <c r="F50" s="14" t="s">
@@ -2617,27 +2628,27 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="30"/>
-      <c r="B51" s="31" t="s">
+      <c r="B51" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="41"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="36"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="30"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="44"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="39"/>
     </row>
     <row r="53" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="30">
@@ -2655,7 +2666,7 @@
         <f>D50+1</f>
         <v>37</v>
       </c>
-      <c r="E53" s="32"/>
+      <c r="E53" s="26"/>
       <c r="F53" s="14" t="s">
         <v>117</v>
       </c>
@@ -2679,7 +2690,7 @@
         <f>D53+1</f>
         <v>38</v>
       </c>
-      <c r="E54" s="32"/>
+      <c r="E54" s="26"/>
       <c r="F54" s="14" t="s">
         <v>118</v>
       </c>
@@ -2720,7 +2731,7 @@
         <f>D54+1</f>
         <v>39</v>
       </c>
-      <c r="E56" s="32" t="s">
+      <c r="E56" s="26" t="s">
         <v>88</v>
       </c>
       <c r="F56" s="14" t="s">
@@ -2748,8 +2759,8 @@
         <f>D56+1</f>
         <v>40</v>
       </c>
-      <c r="E57" s="32"/>
-      <c r="F57" s="45" t="s">
+      <c r="E57" s="26"/>
+      <c r="F57" s="40" t="s">
         <v>104</v>
       </c>
       <c r="G57" s="15"/>
@@ -2770,8 +2781,8 @@
         <f>D57+1</f>
         <v>41</v>
       </c>
-      <c r="E58" s="32"/>
-      <c r="F58" s="46"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="41"/>
       <c r="G58" s="15"/>
       <c r="I58" s="22"/>
     </row>
@@ -2785,8 +2796,8 @@
         <v>46002</v>
       </c>
       <c r="D59" s="12"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="46"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="41"/>
       <c r="G59" s="15"/>
       <c r="H59" s="14" t="s">
         <v>151</v>
@@ -2807,8 +2818,8 @@
         <f>D58+1</f>
         <v>42</v>
       </c>
-      <c r="E60" s="32"/>
-      <c r="F60" s="47"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="42"/>
       <c r="G60" s="15"/>
       <c r="H60" s="14"/>
       <c r="I60" s="14" t="s">
@@ -2825,35 +2836,17 @@
       <c r="C61" s="13">
         <v>46007</v>
       </c>
-      <c r="D61" s="26" t="s">
+      <c r="D61" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="E61" s="27"/>
-      <c r="F61" s="28"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="45"/>
       <c r="G61" s="15"/>
       <c r="H61" s="14"/>
       <c r="I61" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E26:E31"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="E56:E60"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F51:I52"/>
-    <mergeCell ref="E43:E46"/>
-    <mergeCell ref="F57:F60"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="Q10:Q13"/>
     <mergeCell ref="A50:A52"/>
@@ -2870,6 +2863,24 @@
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="E33:E35"/>
     <mergeCell ref="E37:E39"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="E56:E60"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="F51:I52"/>
+    <mergeCell ref="E43:E46"/>
+    <mergeCell ref="F57:F60"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E6:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
